--- a/summary_statistics.xlsx
+++ b/summary_statistics.xlsx
@@ -554,28 +554,28 @@
         <v>0.9019019019019019</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9721936148300721</v>
+        <v>0.9732234809474768</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.999</v>
+        <v>1.037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7487386478304743</v>
+        <v>0.748991935483871</v>
       </c>
       <c r="F4" t="n">
         <v>0.8277608915906788</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.904</v>
+        <v>0.905</v>
       </c>
       <c r="H4" t="n">
-        <v>0.403</v>
+        <v>0.416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3971044467425026</v>
+        <v>0.4115822130299897</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.523</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="5">
@@ -594,7 +594,7 @@
         <v>0.354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1695257315842583</v>
+        <v>0.1703629032258064</v>
       </c>
       <c r="F5" t="n">
         <v>0.1398176291793313</v>
@@ -622,10 +622,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1.653601694915254</v>
+        <v>1.653968253968254</v>
       </c>
       <c r="D6" t="n">
-        <v>1.812812812812813</v>
+        <v>1.796528447444552</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -634,16 +634,16 @@
         <v>1.298653610771114</v>
       </c>
       <c r="G6" t="n">
-        <v>1.569690265486726</v>
+        <v>1.569060773480663</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.369791666666667</v>
+        <v>1.35427135678392</v>
       </c>
       <c r="J6" t="n">
-        <v>1.623326959847036</v>
+        <v>1.613935969868173</v>
       </c>
     </row>
     <row r="7">
@@ -656,28 +656,28 @@
         <v>0.6889567147613762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7316737288135594</v>
+        <v>0.7316825396825396</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.7844544544544544</v>
+        <v>0.7781002892960464</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6659433962264151</v>
+        <v>0.666393001345895</v>
       </c>
       <c r="F7" t="n">
         <v>0.6057772337821297</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6584845132743364</v>
+        <v>0.6584640883977901</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.5090818858560793</v>
+        <v>0.5129086538461538</v>
       </c>
       <c r="I7" t="n">
-        <v>0.48</v>
+        <v>0.4843718592964825</v>
       </c>
       <c r="J7" t="n">
-        <v>0.492906309751434</v>
+        <v>0.4946139359698681</v>
       </c>
     </row>
     <row r="8">
@@ -690,28 +690,28 @@
         <v>0.003977062523122457</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.004011299435028249</v>
+        <v>0.00400705467372134</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00381333714667048</v>
+        <v>0.003673600587776094</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.004687683112621586</v>
+        <v>0.004681373983264088</v>
       </c>
       <c r="F8" t="n">
         <v>0.004257357245489862</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003847633705271258</v>
+        <v>0.003843382176315157</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009171718440807865</v>
+        <v>0.00888510223953262</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.009765625</v>
+        <v>0.009422110552763818</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007170172084130019</v>
+        <v>0.007062146892655367</v>
       </c>
     </row>
     <row r="9">
@@ -724,10 +724,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1.667033935654473</v>
+        <v>1.667107292355144</v>
       </c>
       <c r="D9" t="n">
-        <v>1.856856053001405</v>
+        <v>1.853245718837117</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -736,16 +736,16 @@
         <v>1.317524115755627</v>
       </c>
       <c r="G9" t="n">
-        <v>1.626803164262448</v>
+        <v>1.626220362622036</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.434324659231722</v>
+        <v>1.428921568627451</v>
       </c>
       <c r="J9" t="n">
-        <v>1.705189707806367</v>
+        <v>1.69939446366782</v>
       </c>
     </row>
     <row r="10">
@@ -758,28 +758,28 @@
         <v>0.5978141097424412</v>
       </c>
       <c r="C10" t="n">
-        <v>0.644779638607316</v>
+        <v>0.644800616875964</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.6802328849628588</v>
+        <v>0.6796674631620868</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.595160850599782</v>
+        <v>0.5953157321720196</v>
       </c>
       <c r="F10" t="n">
         <v>0.5435852090032155</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5846300604932527</v>
+        <v>0.584704788470479</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.4790988530857455</v>
+        <v>0.4805081081081081</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4533952912019827</v>
+        <v>0.4550980392156863</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4666375926733537</v>
+        <v>0.4678373702422145</v>
       </c>
     </row>
     <row r="11">
@@ -792,28 +792,28 @@
         <v>1.733295351879265</v>
       </c>
       <c r="C11" t="n">
-        <v>1.483078684588033</v>
+        <v>1.482751943304802</v>
       </c>
       <c r="D11" t="n">
-        <v>1.551057912570896</v>
+        <v>1.539157525004126</v>
       </c>
       <c r="E11" t="n">
-        <v>1.785118105397436</v>
+        <v>1.784538477645051</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1.824831711173681</v>
       </c>
       <c r="G11" t="n">
-        <v>1.812803304711248</v>
+        <v>1.812387918730028</v>
       </c>
       <c r="H11" t="n">
-        <v>1.840735857035199</v>
+        <v>1.827823144417419</v>
       </c>
       <c r="I11" t="n">
-        <v>1.718921978710221</v>
+        <v>1.703501726118563</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.850930315621362</v>
+        <v>1.842840240175003</v>
       </c>
     </row>
     <row r="12">
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1.67811955890888</v>
+        <v>1.678156917363046</v>
       </c>
       <c r="D12" t="n">
-        <v>1.901828098171902</v>
+        <v>1.899829025445037</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -838,16 +838,16 @@
         <v>1.328920270667844</v>
       </c>
       <c r="G12" t="n">
-        <v>1.667591364129779</v>
+        <v>1.667189006750241</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.480701754385965</v>
+        <v>1.477336122733612</v>
       </c>
       <c r="J12" t="n">
-        <v>1.758751182592242</v>
+        <v>1.754881204422489</v>
       </c>
     </row>
     <row r="13">
@@ -860,28 +860,28 @@
         <v>0.5634991520633126</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6059106210098665</v>
+        <v>0.6059261838440111</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.6372245227754773</v>
+        <v>0.6370924268329478</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.5701779801324504</v>
+        <v>0.5703073742246726</v>
       </c>
       <c r="F13" t="n">
         <v>0.5182185937040306</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5570268966349052</v>
+        <v>0.5570865477338477</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.4628501014786894</v>
+        <v>0.4640621403912543</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4421157894736843</v>
+        <v>0.4431555090655508</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4555747398297068</v>
+        <v>0.4563091037402964</v>
       </c>
     </row>
     <row r="14">
@@ -891,31 +891,31 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.263885776005235</v>
+        <v>3.264099617538345</v>
       </c>
       <c r="C14" t="n">
-        <v>2.797252953344368</v>
+        <v>2.797579915703667</v>
       </c>
       <c r="D14" t="n">
-        <v>3.00366224739542</v>
+        <v>2.992895547487907</v>
       </c>
       <c r="E14" t="n">
-        <v>3.380472955668909</v>
+        <v>3.377551295518973</v>
       </c>
       <c r="F14" t="n">
-        <v>3.328429939040569</v>
+        <v>3.328587911298848</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3.398259018685402</v>
+        <v>3.397902263229811</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>3.482241564532599</v>
+        <v>3.471456252648437</v>
       </c>
       <c r="I14" t="n">
-        <v>3.094428421638042</v>
+        <v>3.076262465118787</v>
       </c>
       <c r="J14" t="n">
-        <v>3.408427661015348</v>
+        <v>3.403276938207934</v>
       </c>
     </row>
     <row r="15">
@@ -928,10 +928,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1.725172687124901</v>
+        <v>1.725188246617222</v>
       </c>
       <c r="D15" t="n">
-        <v>1.961947305290152</v>
+        <v>1.961433756805808</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1</v>
@@ -940,16 +940,16 @@
         <v>1.379671758206045</v>
       </c>
       <c r="G15" t="n">
-        <v>1.753341753499632</v>
+        <v>1.753314393939394</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.578846522322284</v>
+        <v>1.576666030169945</v>
       </c>
       <c r="J15" t="n">
-        <v>1.869243331518781</v>
+        <v>1.866992399565689</v>
       </c>
     </row>
     <row r="16">
@@ -962,28 +962,28 @@
         <v>0.5236664966853646</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5514681236553053</v>
+        <v>0.5514787974862707</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.5757831823634032</v>
+        <v>0.5757177033492823</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.5394851025263397</v>
+        <v>0.5395658572479765</v>
       </c>
       <c r="F16" t="n">
         <v>0.4819353266168346</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5174634249026419</v>
+        <v>0.5174994739057239</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.4361712123189351</v>
+        <v>0.4368127438231469</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4217819505652423</v>
+        <v>0.4224212335306474</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4355732172019597</v>
+        <v>0.435972855591748</v>
       </c>
     </row>
     <row r="17">
@@ -993,31 +993,31 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7.75963666791868</v>
+        <v>7.759250326619846</v>
       </c>
       <c r="C17" t="n">
-        <v>6.188062948526606</v>
+        <v>6.189100231008896</v>
       </c>
       <c r="D17" t="n">
-        <v>7.42722302664622</v>
+        <v>7.415769068384292</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>8.069981191689324</v>
+        <v>8.069246272920402</v>
       </c>
       <c r="F17" t="n">
-        <v>6.622985764865787</v>
+        <v>6.62352126968604</v>
       </c>
       <c r="G17" t="n">
-        <v>7.970915938236623</v>
+        <v>7.970137354588209</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.932593540745417</v>
+        <v>7.921229895334744</v>
       </c>
       <c r="I17" t="n">
-        <v>6.243920489367449</v>
+        <v>6.228780038707745</v>
       </c>
       <c r="J17" t="n">
-        <v>7.663749677145055</v>
+        <v>7.656785892535405</v>
       </c>
     </row>
     <row r="18">
@@ -1030,10 +1030,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1.783910595461525</v>
+        <v>1.783919812326722</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0449579735703</v>
+        <v>2.044679196963461</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
@@ -1042,16 +1042,16 @@
         <v>1.453270077939681</v>
       </c>
       <c r="G18" t="n">
-        <v>1.875065310262163</v>
+        <v>1.875007681435507</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.687413766671777</v>
+        <v>1.685369209600978</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0332999666333</v>
+        <v>2.031574740207834</v>
       </c>
     </row>
     <row r="19">
@@ -1061,31 +1061,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4970567828663663</v>
+        <v>0.4970554083353409</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.5222099471080021</v>
+        <v>0.5222192365109831</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5203545335867897</v>
+        <v>0.520391686102346</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.5172692554370009</v>
+        <v>0.5173265538040152</v>
       </c>
       <c r="F19" t="n">
         <v>0.4657363605557439</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4822125580108799</v>
+        <v>0.4822325324156578</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.4164725770097671</v>
+        <v>0.4168823573517283</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4107036639583014</v>
+        <v>0.4112459868521633</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4162135468802136</v>
+        <v>0.4164928057553957</v>
       </c>
     </row>
     <row r="20">
@@ -1095,31 +1095,31 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>14.7649801288725</v>
+        <v>14.76468259323918</v>
       </c>
       <c r="C20" t="n">
-        <v>8.947043112881127</v>
+        <v>8.946946834216421</v>
       </c>
       <c r="D20" t="n">
-        <v>13.58829948928649</v>
+        <v>13.57833805742203</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15.4645836027482</v>
+        <v>15.46370947053022</v>
       </c>
       <c r="F20" t="n">
-        <v>8.756493931279191</v>
+        <v>8.756314078977129</v>
       </c>
       <c r="G20" t="n">
-        <v>14.0179650515299</v>
+        <v>14.01767428458036</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>14.31565747081246</v>
+        <v>14.30224381145495</v>
       </c>
       <c r="I20" t="n">
-        <v>8.518548211504502</v>
+        <v>8.498153856319762</v>
       </c>
       <c r="J20" t="n">
-        <v>13.06448447511515</v>
+        <v>13.05844628189882</v>
       </c>
     </row>
     <row r="21">
@@ -1132,10 +1132,10 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1.827278903408864</v>
+        <v>1.827285805626598</v>
       </c>
       <c r="D21" t="n">
-        <v>2.265511559231886</v>
+        <v>2.265053369184388</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
@@ -1144,16 +1144,16 @@
         <v>1.503651522006075</v>
       </c>
       <c r="G21" t="n">
-        <v>2.113629375851013</v>
+        <v>2.113579975848062</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.793637505232315</v>
+        <v>1.791510090466249</v>
       </c>
       <c r="J21" t="n">
-        <v>2.259232613908873</v>
+        <v>2.257723071028306</v>
       </c>
     </row>
     <row r="22">
@@ -1163,31 +1163,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4737008955765517</v>
+        <v>0.4736998924299174</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.5137101866283019</v>
+        <v>0.513719229539642</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4854898601797922</v>
+        <v>0.4855562617127027</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.4954685834373954</v>
+        <v>0.4955037980849736</v>
       </c>
       <c r="F22" t="n">
         <v>0.460674723712273</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4563974173145341</v>
+        <v>0.456413876385992</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3986383519119515</v>
+        <v>0.3989177001127396</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.4060820426956886</v>
+        <v>0.4065873347251218</v>
       </c>
       <c r="J22" t="n">
-        <v>0.401115587529976</v>
+        <v>0.4013396235451889</v>
       </c>
     </row>
     <row r="23">
@@ -1197,31 +1197,31 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>27.93780109745781</v>
+        <v>27.93763768015817</v>
       </c>
       <c r="C23" t="n">
-        <v>10.30944637548575</v>
+        <v>10.30905856243352</v>
       </c>
       <c r="D23" t="n">
-        <v>20.08258498874277</v>
+        <v>20.07385244492147</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>29.64740706061016</v>
+        <v>29.64695203896099</v>
       </c>
       <c r="F23" t="n">
-        <v>9.909702514130799</v>
+        <v>9.911384323393028</v>
       </c>
       <c r="G23" t="n">
-        <v>20.86183069584528</v>
+        <v>20.8611295330352</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>24.74402635302066</v>
+        <v>24.72970891378657</v>
       </c>
       <c r="I23" t="n">
-        <v>9.883019016343919</v>
+        <v>9.861593999364898</v>
       </c>
       <c r="J23" t="n">
-        <v>19.49042506336145</v>
+        <v>19.48691024490435</v>
       </c>
     </row>
   </sheetData>
